--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/PerformanceInfo.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/PerformanceInfo.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\nyxp\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -19,15 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
-  <si>
-    <t>生效起始日*</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>子产品代码*</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>数据状态</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -171,7 +163,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -180,9 +172,6 @@
     </xf>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -462,7 +451,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr defaultColWidth="12" defaultRowHeight="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="12.08984375" bestFit="1" customWidth="1"/>
@@ -471,12 +460,12 @@
     <col min="6" max="7" width="29" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:10" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -484,10 +473,10 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
@@ -496,17 +485,11 @@
       <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/PerformanceInfo.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/PerformanceInfo.xlsx
@@ -37,53 +37,27 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>中债新综合全价指数收益率【系数】%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>中债新综合财富指数（1-3年）收益率【系数】</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>%</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>中证501指数收益率【系数】%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>沪深300指数收益率【系数】</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>%</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>更新时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>更新人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中债新综合全价指数收益率【系数】</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中债新综合财富指数（1-3年）收益率【系数】</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中证501指数收益率【系数】</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>沪深300指数收益率【系数】</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -474,22 +448,22 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/PerformanceInfo.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/PerformanceInfo.xlsx
@@ -45,19 +45,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>中债新综合全价指数收益率【系数】</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>中债新综合财富指数（1-3年）收益率【系数】</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>中证501指数收益率【系数】</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>沪深300指数收益率【系数】</t>
+    <t>中债新综合全价指数收益率【系数】(%)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中债新综合财富指数（1-3年）收益率【系数】(%)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中证501指数收益率【系数】(%)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>沪深300指数收益率【系数】(%)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/PerformanceInfo.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/PerformanceInfo.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\nyxp\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Git\NY\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>数据状态</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -58,6 +58,10 @@
   </si>
   <si>
     <t>沪深300指数收益率【系数】(%)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>子产品名称</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -425,16 +429,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J1"/>
-  <sheetFormatPr defaultColWidth="12" defaultRowHeight="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:K1"/>
+  <sheetFormatPr defaultColWidth="12" defaultRowHeight="19.5" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="3" width="12.08984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="32.08984375" customWidth="1"/>
-    <col min="5" max="5" width="43.6328125" customWidth="1"/>
-    <col min="6" max="7" width="29" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.125" customWidth="1"/>
+    <col min="4" max="4" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="32.125" customWidth="1"/>
+    <col min="6" max="6" width="43.625" customWidth="1"/>
+    <col min="7" max="8" width="29" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="36.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -442,27 +448,30 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>5</v>
       </c>
     </row>
